--- a/WorkBot/refactor/data/orders/Performance Food/Performance Food_Collegetown_2025-10-24.xlsx
+++ b/WorkBot/refactor/data/orders/Performance Food/Performance Food_Collegetown_2025-10-24.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1064,6 +1064,60 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TN380</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Natalie's - Strawberry Lemonade</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>10.15</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>10.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TN362</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Natalie's - Orange Pineapple</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>13.38</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>13.38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
